--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2559,6 +2559,40 @@
         <v>42</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>12:10:57</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>44</v>
+      </c>
+      <c r="D63" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>42</v>
+      </c>
+      <c r="F63" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H63" t="n">
+        <v>39</v>
+      </c>
+      <c r="I63" t="n">
+        <v>42</v>
+      </c>
+      <c r="J63" t="n">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2593,6 +2593,40 @@
         <v>42</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>12:58:52</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>44</v>
+      </c>
+      <c r="D64" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>42</v>
+      </c>
+      <c r="F64" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H64" t="n">
+        <v>39</v>
+      </c>
+      <c r="I64" t="n">
+        <v>42</v>
+      </c>
+      <c r="J64" t="n">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -2599,7 +2599,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12:58:52</t>
+          <t>17:55:03</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2612,7 +2612,7 @@
         <v>42</v>
       </c>
       <c r="F64" t="n">
-        <v>41.5</v>
+        <v>41.25</v>
       </c>
       <c r="G64" t="n">
         <v>36.75</v>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2627,6 +2627,40 @@
         <v>42</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>12:24:20</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>44</v>
+      </c>
+      <c r="D65" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>42</v>
+      </c>
+      <c r="F65" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G65" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H65" t="n">
+        <v>39</v>
+      </c>
+      <c r="I65" t="n">
+        <v>42</v>
+      </c>
+      <c r="J65" t="n">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2661,6 +2661,40 @@
         <v>42</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>12:25:56</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>44</v>
+      </c>
+      <c r="D66" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>42</v>
+      </c>
+      <c r="F66" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G66" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H66" t="n">
+        <v>39</v>
+      </c>
+      <c r="I66" t="n">
+        <v>42</v>
+      </c>
+      <c r="J66" t="n">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2695,6 +2695,40 @@
         <v>42</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>12:24:55</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>44</v>
+      </c>
+      <c r="D67" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>42</v>
+      </c>
+      <c r="F67" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G67" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H67" t="n">
+        <v>39</v>
+      </c>
+      <c r="I67" t="n">
+        <v>42</v>
+      </c>
+      <c r="J67" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2729,6 +2729,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>12:24:38</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>44</v>
+      </c>
+      <c r="D68" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E68" t="n">
+        <v>42</v>
+      </c>
+      <c r="F68" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G68" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H68" t="n">
+        <v>39</v>
+      </c>
+      <c r="I68" t="n">
+        <v>42</v>
+      </c>
+      <c r="J68" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2763,6 +2763,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>12:03:09</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>44</v>
+      </c>
+      <c r="D69" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>42</v>
+      </c>
+      <c r="F69" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G69" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H69" t="n">
+        <v>39</v>
+      </c>
+      <c r="I69" t="n">
+        <v>42</v>
+      </c>
+      <c r="J69" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2797,6 +2797,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>13:01:59</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>44</v>
+      </c>
+      <c r="D70" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>42</v>
+      </c>
+      <c r="F70" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G70" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H70" t="n">
+        <v>39</v>
+      </c>
+      <c r="I70" t="n">
+        <v>42</v>
+      </c>
+      <c r="J70" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2831,6 +2831,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>13:21:46</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>44</v>
+      </c>
+      <c r="D71" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E71" t="n">
+        <v>42</v>
+      </c>
+      <c r="F71" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G71" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H71" t="n">
+        <v>39</v>
+      </c>
+      <c r="I71" t="n">
+        <v>42</v>
+      </c>
+      <c r="J71" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2865,6 +2865,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>12:48:22</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>44</v>
+      </c>
+      <c r="D72" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>42</v>
+      </c>
+      <c r="F72" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G72" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H72" t="n">
+        <v>39</v>
+      </c>
+      <c r="I72" t="n">
+        <v>42</v>
+      </c>
+      <c r="J72" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2899,6 +2899,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>12:43:48</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>44</v>
+      </c>
+      <c r="D73" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>42</v>
+      </c>
+      <c r="F73" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G73" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H73" t="n">
+        <v>39</v>
+      </c>
+      <c r="I73" t="n">
+        <v>42</v>
+      </c>
+      <c r="J73" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2933,6 +2933,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>12:51:43</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>44</v>
+      </c>
+      <c r="D74" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>42</v>
+      </c>
+      <c r="F74" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G74" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H74" t="n">
+        <v>39</v>
+      </c>
+      <c r="I74" t="n">
+        <v>42</v>
+      </c>
+      <c r="J74" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2967,6 +2967,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>12:25:27</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>44</v>
+      </c>
+      <c r="D75" t="n">
+        <v>38</v>
+      </c>
+      <c r="E75" t="n">
+        <v>42</v>
+      </c>
+      <c r="F75" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H75" t="n">
+        <v>39</v>
+      </c>
+      <c r="I75" t="n">
+        <v>42</v>
+      </c>
+      <c r="J75" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3001,6 +3001,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>12:13:22</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>44</v>
+      </c>
+      <c r="D76" t="n">
+        <v>38</v>
+      </c>
+      <c r="E76" t="n">
+        <v>42</v>
+      </c>
+      <c r="F76" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G76" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H76" t="n">
+        <v>39</v>
+      </c>
+      <c r="I76" t="n">
+        <v>42</v>
+      </c>
+      <c r="J76" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3035,6 +3035,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>12:37:46</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>44</v>
+      </c>
+      <c r="D77" t="n">
+        <v>38</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G77" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H77" t="n">
+        <v>39</v>
+      </c>
+      <c r="I77" t="n">
+        <v>42</v>
+      </c>
+      <c r="J77" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12:37:46</t>
+          <t>16:30:39</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -3051,7 +3051,7 @@
         <v>38</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F77" t="n">
         <v>41.75</v>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3069,6 +3069,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>10:54:27</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>44</v>
+      </c>
+      <c r="D78" t="n">
+        <v>38</v>
+      </c>
+      <c r="E78" t="n">
+        <v>42</v>
+      </c>
+      <c r="F78" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G78" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H78" t="n">
+        <v>39</v>
+      </c>
+      <c r="I78" t="n">
+        <v>42</v>
+      </c>
+      <c r="J78" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>10:54:27</t>
+          <t>13:26:21</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -3088,7 +3088,7 @@
         <v>42</v>
       </c>
       <c r="F78" t="n">
-        <v>41.75</v>
+        <v>41.25</v>
       </c>
       <c r="G78" t="n">
         <v>36.75</v>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3103,6 +3103,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>10:21:52</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>44</v>
+      </c>
+      <c r="D79" t="n">
+        <v>38</v>
+      </c>
+      <c r="E79" t="n">
+        <v>42</v>
+      </c>
+      <c r="F79" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G79" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H79" t="n">
+        <v>39</v>
+      </c>
+      <c r="I79" t="n">
+        <v>42</v>
+      </c>
+      <c r="J79" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3137,6 +3137,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>11:38:44</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>44</v>
+      </c>
+      <c r="D80" t="n">
+        <v>38</v>
+      </c>
+      <c r="E80" t="n">
+        <v>42</v>
+      </c>
+      <c r="F80" t="n">
+        <v>42</v>
+      </c>
+      <c r="G80" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H80" t="n">
+        <v>39</v>
+      </c>
+      <c r="I80" t="n">
+        <v>42</v>
+      </c>
+      <c r="J80" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3171,6 +3171,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>12:44:15</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>44</v>
+      </c>
+      <c r="D81" t="n">
+        <v>38</v>
+      </c>
+      <c r="E81" t="n">
+        <v>42</v>
+      </c>
+      <c r="F81" t="n">
+        <v>42</v>
+      </c>
+      <c r="G81" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H81" t="n">
+        <v>39</v>
+      </c>
+      <c r="I81" t="n">
+        <v>42</v>
+      </c>
+      <c r="J81" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3205,6 +3205,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>13:02:02</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>44</v>
+      </c>
+      <c r="D82" t="n">
+        <v>38</v>
+      </c>
+      <c r="E82" t="n">
+        <v>42</v>
+      </c>
+      <c r="F82" t="n">
+        <v>42</v>
+      </c>
+      <c r="G82" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H82" t="n">
+        <v>39</v>
+      </c>
+      <c r="I82" t="n">
+        <v>42</v>
+      </c>
+      <c r="J82" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3239,6 +3239,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>12:43:51</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>44</v>
+      </c>
+      <c r="D83" t="n">
+        <v>38</v>
+      </c>
+      <c r="E83" t="n">
+        <v>42</v>
+      </c>
+      <c r="F83" t="n">
+        <v>42</v>
+      </c>
+      <c r="G83" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H83" t="n">
+        <v>39</v>
+      </c>
+      <c r="I83" t="n">
+        <v>42</v>
+      </c>
+      <c r="J83" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3273,6 +3273,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>13:23:19</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>44</v>
+      </c>
+      <c r="D84" t="n">
+        <v>38</v>
+      </c>
+      <c r="E84" t="n">
+        <v>42</v>
+      </c>
+      <c r="F84" t="n">
+        <v>42</v>
+      </c>
+      <c r="G84" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H84" t="n">
+        <v>39</v>
+      </c>
+      <c r="I84" t="n">
+        <v>42</v>
+      </c>
+      <c r="J84" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3307,6 +3307,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>14:29:42</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>44</v>
+      </c>
+      <c r="D85" t="n">
+        <v>38</v>
+      </c>
+      <c r="E85" t="n">
+        <v>42</v>
+      </c>
+      <c r="F85" t="n">
+        <v>42</v>
+      </c>
+      <c r="G85" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H85" t="n">
+        <v>39</v>
+      </c>
+      <c r="I85" t="n">
+        <v>42</v>
+      </c>
+      <c r="J85" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3341,6 +3341,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>14:10:18</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>44</v>
+      </c>
+      <c r="D86" t="n">
+        <v>38</v>
+      </c>
+      <c r="E86" t="n">
+        <v>42</v>
+      </c>
+      <c r="F86" t="n">
+        <v>42</v>
+      </c>
+      <c r="G86" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H86" t="n">
+        <v>39</v>
+      </c>
+      <c r="I86" t="n">
+        <v>42</v>
+      </c>
+      <c r="J86" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3375,6 +3375,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>13:56:46</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>44</v>
+      </c>
+      <c r="D87" t="n">
+        <v>38</v>
+      </c>
+      <c r="E87" t="n">
+        <v>42</v>
+      </c>
+      <c r="F87" t="n">
+        <v>42</v>
+      </c>
+      <c r="G87" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H87" t="n">
+        <v>39</v>
+      </c>
+      <c r="I87" t="n">
+        <v>42</v>
+      </c>
+      <c r="J87" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3409,6 +3409,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>14:25:02</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>44</v>
+      </c>
+      <c r="D88" t="n">
+        <v>38</v>
+      </c>
+      <c r="E88" t="n">
+        <v>42</v>
+      </c>
+      <c r="F88" t="n">
+        <v>42</v>
+      </c>
+      <c r="G88" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H88" t="n">
+        <v>39</v>
+      </c>
+      <c r="I88" t="n">
+        <v>42</v>
+      </c>
+      <c r="J88" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -3415,7 +3415,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>14:25:02</t>
+          <t>19:10:01</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -3434,7 +3434,7 @@
         <v>36.75</v>
       </c>
       <c r="H88" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I88" t="n">
         <v>42</v>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3443,6 +3443,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>13:54:49</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>44</v>
+      </c>
+      <c r="D89" t="n">
+        <v>38</v>
+      </c>
+      <c r="E89" t="n">
+        <v>42</v>
+      </c>
+      <c r="F89" t="n">
+        <v>42</v>
+      </c>
+      <c r="G89" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H89" t="n">
+        <v>38</v>
+      </c>
+      <c r="I89" t="n">
+        <v>42</v>
+      </c>
+      <c r="J89" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3477,6 +3477,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>13:15:10</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>44</v>
+      </c>
+      <c r="D90" t="n">
+        <v>38</v>
+      </c>
+      <c r="E90" t="n">
+        <v>42</v>
+      </c>
+      <c r="F90" t="n">
+        <v>42</v>
+      </c>
+      <c r="G90" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>42</v>
+      </c>
+      <c r="J90" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>13:15:10</t>
+          <t>17:11:19</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -3502,7 +3502,7 @@
         <v>36.75</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I90" t="n">
         <v>42</v>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3511,6 +3511,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>13:57:25</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>44</v>
+      </c>
+      <c r="D91" t="n">
+        <v>38</v>
+      </c>
+      <c r="E91" t="n">
+        <v>42</v>
+      </c>
+      <c r="F91" t="n">
+        <v>42</v>
+      </c>
+      <c r="G91" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H91" t="n">
+        <v>38</v>
+      </c>
+      <c r="I91" t="n">
+        <v>42</v>
+      </c>
+      <c r="J91" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3545,6 +3545,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>15:05:14</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>44</v>
+      </c>
+      <c r="D92" t="n">
+        <v>38</v>
+      </c>
+      <c r="E92" t="n">
+        <v>42</v>
+      </c>
+      <c r="F92" t="n">
+        <v>42</v>
+      </c>
+      <c r="G92" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H92" t="n">
+        <v>38</v>
+      </c>
+      <c r="I92" t="n">
+        <v>42</v>
+      </c>
+      <c r="J92" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3579,6 +3579,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>12:23:50</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>44</v>
+      </c>
+      <c r="D93" t="n">
+        <v>38</v>
+      </c>
+      <c r="E93" t="n">
+        <v>42</v>
+      </c>
+      <c r="F93" t="n">
+        <v>42</v>
+      </c>
+      <c r="G93" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H93" t="n">
+        <v>38</v>
+      </c>
+      <c r="I93" t="n">
+        <v>42</v>
+      </c>
+      <c r="J93" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3613,6 +3613,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>14:34:40</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>44</v>
+      </c>
+      <c r="D94" t="n">
+        <v>38</v>
+      </c>
+      <c r="E94" t="n">
+        <v>42</v>
+      </c>
+      <c r="F94" t="n">
+        <v>42</v>
+      </c>
+      <c r="G94" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H94" t="n">
+        <v>38</v>
+      </c>
+      <c r="I94" t="n">
+        <v>42</v>
+      </c>
+      <c r="J94" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3647,6 +3647,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>14:56:28</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>44</v>
+      </c>
+      <c r="D95" t="n">
+        <v>38</v>
+      </c>
+      <c r="E95" t="n">
+        <v>42</v>
+      </c>
+      <c r="F95" t="n">
+        <v>42</v>
+      </c>
+      <c r="G95" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H95" t="n">
+        <v>38</v>
+      </c>
+      <c r="I95" t="n">
+        <v>42</v>
+      </c>
+      <c r="J95" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3681,6 +3681,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>14:41:44</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>44</v>
+      </c>
+      <c r="D96" t="n">
+        <v>38</v>
+      </c>
+      <c r="E96" t="n">
+        <v>42</v>
+      </c>
+      <c r="F96" t="n">
+        <v>42</v>
+      </c>
+      <c r="G96" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H96" t="n">
+        <v>38</v>
+      </c>
+      <c r="I96" t="n">
+        <v>42</v>
+      </c>
+      <c r="J96" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3715,6 +3715,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>13:59:23</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>44</v>
+      </c>
+      <c r="D97" t="n">
+        <v>38</v>
+      </c>
+      <c r="E97" t="n">
+        <v>42</v>
+      </c>
+      <c r="F97" t="n">
+        <v>42</v>
+      </c>
+      <c r="G97" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H97" t="n">
+        <v>38</v>
+      </c>
+      <c r="I97" t="n">
+        <v>42</v>
+      </c>
+      <c r="J97" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3749,6 +3749,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>14:16:13</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>44</v>
+      </c>
+      <c r="D98" t="n">
+        <v>38</v>
+      </c>
+      <c r="E98" t="n">
+        <v>42</v>
+      </c>
+      <c r="F98" t="n">
+        <v>42</v>
+      </c>
+      <c r="G98" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H98" t="n">
+        <v>38</v>
+      </c>
+      <c r="I98" t="n">
+        <v>42</v>
+      </c>
+      <c r="J98" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3783,6 +3783,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>15:48:56</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>44</v>
+      </c>
+      <c r="D99" t="n">
+        <v>38</v>
+      </c>
+      <c r="E99" t="n">
+        <v>42</v>
+      </c>
+      <c r="F99" t="n">
+        <v>42</v>
+      </c>
+      <c r="G99" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H99" t="n">
+        <v>38</v>
+      </c>
+      <c r="I99" t="n">
+        <v>42</v>
+      </c>
+      <c r="J99" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3817,6 +3817,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>15:29:43</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>44</v>
+      </c>
+      <c r="D100" t="n">
+        <v>38</v>
+      </c>
+      <c r="E100" t="n">
+        <v>42</v>
+      </c>
+      <c r="F100" t="n">
+        <v>42</v>
+      </c>
+      <c r="G100" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H100" t="n">
+        <v>38</v>
+      </c>
+      <c r="I100" t="n">
+        <v>42</v>
+      </c>
+      <c r="J100" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3851,6 +3851,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>12:57:09</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>44</v>
+      </c>
+      <c r="D101" t="n">
+        <v>38</v>
+      </c>
+      <c r="E101" t="n">
+        <v>42</v>
+      </c>
+      <c r="F101" t="n">
+        <v>42</v>
+      </c>
+      <c r="G101" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H101" t="n">
+        <v>38</v>
+      </c>
+      <c r="I101" t="n">
+        <v>42</v>
+      </c>
+      <c r="J101" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -3857,7 +3857,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>12:57:09</t>
+          <t>17:24:34</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -3879,7 +3879,7 @@
         <v>38</v>
       </c>
       <c r="I101" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J101" t="n">
         <v>41</v>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3885,6 +3885,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>12:38:48</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>44</v>
+      </c>
+      <c r="D102" t="n">
+        <v>38</v>
+      </c>
+      <c r="E102" t="n">
+        <v>42</v>
+      </c>
+      <c r="F102" t="n">
+        <v>42</v>
+      </c>
+      <c r="G102" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H102" t="n">
+        <v>38</v>
+      </c>
+      <c r="I102" t="n">
+        <v>41</v>
+      </c>
+      <c r="J102" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3919,6 +3919,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>12:31:51</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>44</v>
+      </c>
+      <c r="D103" t="n">
+        <v>38</v>
+      </c>
+      <c r="E103" t="n">
+        <v>42</v>
+      </c>
+      <c r="F103" t="n">
+        <v>42</v>
+      </c>
+      <c r="G103" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H103" t="n">
+        <v>38</v>
+      </c>
+      <c r="I103" t="n">
+        <v>41</v>
+      </c>
+      <c r="J103" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3953,6 +3953,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>12:02:38</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>44</v>
+      </c>
+      <c r="D104" t="n">
+        <v>38</v>
+      </c>
+      <c r="E104" t="n">
+        <v>42</v>
+      </c>
+      <c r="F104" t="n">
+        <v>42</v>
+      </c>
+      <c r="G104" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H104" t="n">
+        <v>38</v>
+      </c>
+      <c r="I104" t="n">
+        <v>41</v>
+      </c>
+      <c r="J104" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3987,6 +3987,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>12:21:18</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>44</v>
+      </c>
+      <c r="D105" t="n">
+        <v>38</v>
+      </c>
+      <c r="E105" t="n">
+        <v>42</v>
+      </c>
+      <c r="F105" t="n">
+        <v>42</v>
+      </c>
+      <c r="G105" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H105" t="n">
+        <v>38</v>
+      </c>
+      <c r="I105" t="n">
+        <v>41</v>
+      </c>
+      <c r="J105" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4021,6 +4021,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>13:33:09</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>44</v>
+      </c>
+      <c r="D106" t="n">
+        <v>38</v>
+      </c>
+      <c r="E106" t="n">
+        <v>42</v>
+      </c>
+      <c r="F106" t="n">
+        <v>42</v>
+      </c>
+      <c r="G106" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H106" t="n">
+        <v>38</v>
+      </c>
+      <c r="I106" t="n">
+        <v>41</v>
+      </c>
+      <c r="J106" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4055,6 +4055,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>12:49:51</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>44</v>
+      </c>
+      <c r="D107" t="n">
+        <v>38</v>
+      </c>
+      <c r="E107" t="n">
+        <v>42</v>
+      </c>
+      <c r="F107" t="n">
+        <v>42</v>
+      </c>
+      <c r="G107" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H107" t="n">
+        <v>38</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>12:49:51</t>
+          <t>17:11:16</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -4083,7 +4083,7 @@
         <v>38</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J107" t="n">
         <v>41</v>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4089,6 +4089,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>12:51:49</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>44</v>
+      </c>
+      <c r="D108" t="n">
+        <v>38</v>
+      </c>
+      <c r="E108" t="n">
+        <v>42</v>
+      </c>
+      <c r="F108" t="n">
+        <v>42</v>
+      </c>
+      <c r="G108" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H108" t="n">
+        <v>38</v>
+      </c>
+      <c r="I108" t="n">
+        <v>41</v>
+      </c>
+      <c r="J108" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4123,6 +4123,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>12:52:38</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>44</v>
+      </c>
+      <c r="D109" t="n">
+        <v>38</v>
+      </c>
+      <c r="E109" t="n">
+        <v>42</v>
+      </c>
+      <c r="F109" t="n">
+        <v>42</v>
+      </c>
+      <c r="G109" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H109" t="n">
+        <v>38</v>
+      </c>
+      <c r="I109" t="n">
+        <v>41</v>
+      </c>
+      <c r="J109" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4157,6 +4157,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>07:32:30</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>44</v>
+      </c>
+      <c r="D110" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E110" t="n">
+        <v>42</v>
+      </c>
+      <c r="F110" t="n">
+        <v>42</v>
+      </c>
+      <c r="G110" t="n">
+        <v>36</v>
+      </c>
+      <c r="H110" t="n">
+        <v>38</v>
+      </c>
+      <c r="I110" t="n">
+        <v>41</v>
+      </c>
+      <c r="J110" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>07:32:30</t>
+          <t>12:08:29</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D110" t="n">
         <v>37.5</v>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4191,6 +4191,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>12:19:39</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>43</v>
+      </c>
+      <c r="D111" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E111" t="n">
+        <v>42</v>
+      </c>
+      <c r="F111" t="n">
+        <v>42</v>
+      </c>
+      <c r="G111" t="n">
+        <v>36</v>
+      </c>
+      <c r="H111" t="n">
+        <v>37</v>
+      </c>
+      <c r="I111" t="n">
+        <v>41</v>
+      </c>
+      <c r="J111" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4225,6 +4225,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>12:36:19</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>43</v>
+      </c>
+      <c r="D112" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>42</v>
+      </c>
+      <c r="G112" t="n">
+        <v>36</v>
+      </c>
+      <c r="H112" t="n">
+        <v>37</v>
+      </c>
+      <c r="I112" t="n">
+        <v>41</v>
+      </c>
+      <c r="J112" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4259,6 +4259,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>13:48:01</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>43</v>
+      </c>
+      <c r="D113" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E113" t="n">
+        <v>41</v>
+      </c>
+      <c r="F113" t="n">
+        <v>42</v>
+      </c>
+      <c r="G113" t="n">
+        <v>36</v>
+      </c>
+      <c r="H113" t="n">
+        <v>37</v>
+      </c>
+      <c r="I113" t="n">
+        <v>41</v>
+      </c>
+      <c r="J113" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4293,6 +4293,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>12:26:39</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>43</v>
+      </c>
+      <c r="D114" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E114" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F114" t="n">
+        <v>41</v>
+      </c>
+      <c r="G114" t="n">
+        <v>36</v>
+      </c>
+      <c r="H114" t="n">
+        <v>37</v>
+      </c>
+      <c r="I114" t="n">
+        <v>41</v>
+      </c>
+      <c r="J114" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4327,6 +4327,40 @@
         <v>41</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>14:01:46</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>43</v>
+      </c>
+      <c r="D115" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E115" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F115" t="n">
+        <v>41</v>
+      </c>
+      <c r="G115" t="n">
+        <v>36</v>
+      </c>
+      <c r="H115" t="n">
+        <v>37</v>
+      </c>
+      <c r="I115" t="n">
+        <v>41</v>
+      </c>
+      <c r="J115" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4361,6 +4361,40 @@
         <v>40</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>14:19:51</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>43</v>
+      </c>
+      <c r="D116" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E116" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F116" t="n">
+        <v>41</v>
+      </c>
+      <c r="G116" t="n">
+        <v>36</v>
+      </c>
+      <c r="H116" t="n">
+        <v>37</v>
+      </c>
+      <c r="I116" t="n">
+        <v>41</v>
+      </c>
+      <c r="J116" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4395,6 +4395,40 @@
         <v>40</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>14:12:27</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>43</v>
+      </c>
+      <c r="D117" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E117" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F117" t="n">
+        <v>41</v>
+      </c>
+      <c r="G117" t="n">
+        <v>36</v>
+      </c>
+      <c r="H117" t="n">
+        <v>37</v>
+      </c>
+      <c r="I117" t="n">
+        <v>41</v>
+      </c>
+      <c r="J117" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_rates.xlsx
+++ b/historical_rates.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4429,6 +4429,40 @@
         <v>40</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>13:44:49</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>43</v>
+      </c>
+      <c r="D118" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E118" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F118" t="n">
+        <v>41</v>
+      </c>
+      <c r="G118" t="n">
+        <v>36</v>
+      </c>
+      <c r="H118" t="n">
+        <v>37</v>
+      </c>
+      <c r="I118" t="n">
+        <v>41</v>
+      </c>
+      <c r="J118" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
